--- a/www/download/COUNTRY.LVA.zdW16.xlsx
+++ b/www/download/COUNTRY.LVA.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Letônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.866079123270384</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.897582942675166</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.872579672483692</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.811770755372418</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.76926670738406</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.80224796578597</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.781997950654569</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.729871412808954</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.680917298409343</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.717395923910311</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.753527751960198</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.71261308609804</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.774285339236056</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.75302585744013</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.75281950437192</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.924</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.942</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.957</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.966</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.977</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.035</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.069</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.057</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.901</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.836</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.848</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.892</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.898</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.784</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.798</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.838</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.843</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.861</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.911</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.949</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.795</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.773</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.785</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.791</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1816.292</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1860.284</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1859.229</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1866.59</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1826.228</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1855.1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1967.37</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1998.781</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2103.105</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1750.493</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1610.913</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1645.547</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1690.105</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1714.481</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1723.085</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1535.709</t>
+          <t>1841406992.94523</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1571.557</t>
+          <t>1936923789.13775</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1589.281</t>
+          <t>1957990425.94009</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1615.794</t>
+          <t>2055356652.11087</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1583.963</t>
+          <t>1985675187.85459</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1634.536</t>
+          <t>1992562513.75745</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1728.467</t>
+          <t>2190263016.94049</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1770.056</t>
+          <t>2137406764.1883</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1880.672</t>
+          <t>2125181390.6093</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1541.993</t>
+          <t>1600803743.1539</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1420.831</t>
+          <t>1461411689.41951</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1454.661</t>
+          <t>1596034056.94888</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1491.285</t>
+          <t>1665890147.92452</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1509.355</t>
+          <t>1647396701.20507</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1520.214</t>
+          <t>1704145258.79232</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>502298113.947982</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>522513093.592771</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>519482441.418896</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>555588381.574627</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>538630327.490354</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>558112098.828598</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>650202346.124843</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>709695975.516289</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>705430275.80751</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>496375643.829363</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>382138506.608908</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>401125712.900103</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>408792753.602851</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>414005979.162035</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>458546206.76313</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6058664.04934072</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5897463.94638535</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5423811.04573334</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4408654.12426687</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3532264.86603983</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3154009.47591689</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2724216.1635224</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1943494.21007044</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1735997.48591194</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1829258.35407124</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1702667.85580115</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1539379.70527571</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1640970.08658442</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1508382.05120459</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1502982.47079075</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>9861.13523923107</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10131.8746422468</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9997.00231969213</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>10831.5438603768</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>11211.0332429619</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>12014.5187554189</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>13787.7908335468</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>14863.6876774351</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>16788.2377643186</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>12215.9622520338</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>12417.3449013965</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>13823.0079030969</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13779.7931207139</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>13820.6522766306</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>13736.1806043414</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16704.0285232624</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17313.2139833202</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>17630.254630949</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>20148.5412920229</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>21451.3313017198</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>23249.5885053083</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>27005.7450824333</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>29563.1136151023</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>32058.9397152833</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>22069.2632313742</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>22259.5543638835</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>25919.9438265152</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>26427.1654781833</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>25982.2583161253</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>26971.1095028251</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.05736565070805</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.00768922209023</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.05935460620978</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.90825736027917</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.94072375645867</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.92868763001317</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.65835245028187</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.4941046040346</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.66599274867695</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2.10650415500662</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.71810475894836</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.62644665554579</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.64802210131349</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.64573237095511</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.31529075495176</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.866079123270384</t>
+          <t>640.898912838419</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.897582942675166</t>
+          <t>654.376502639696</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.872579672483692</t>
+          <t>632.982540811873</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.811770755372418</t>
+          <t>662.795564061589</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.76926670738406</t>
+          <t>639.217610711994</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.80224796578597</t>
+          <t>648.02565901724</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.781997950654569</t>
+          <t>713.911838601655</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729871412808954</t>
+          <t>748.221922295273</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.680917298409343</t>
+          <t>745.642791556132</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717395923910311</t>
+          <t>624.411150172165</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.753527751960198</t>
+          <t>518.31555143829</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.71261308609804</t>
+          <t>535.112542388846</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.774285339236056</t>
+          <t>529.037741976746</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75302585744013</t>
+          <t>527.530554487812</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.75281950437192</t>
+          <t>579.975724122699</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>80518333.3945412</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>51329871.1632676</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>80993201.9771669</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>121151053.514956</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>116172620.081493</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>117565211.668344</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>124381418.977728</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>155796185.020578</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>158787053.1688</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>175161956.289247</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>132215789.957161</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>158991832.277752</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>164255998.314189</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>163782048.955247</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>235096083.27427</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>70385494.9655326</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>38694125.6722012</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>60019060.5881018</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>95386043.5725996</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>86778085.0246826</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>61018788.0320567</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>60682557.0219302</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>59692835.8094321</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>40717610.3510647</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>79206536.9523651</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>58670355.3495507</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>70441604.6053712</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>76111388.1848992</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>57861503.1878776</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>123480650.955912</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>10132838.4290086</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>12635745.4910665</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>20974141.3890651</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>25765009.9423562</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>29394535.0568108</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>56546423.6362878</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>63698861.9557978</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>96103349.2111455</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>118069442.817735</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>95955419.3368816</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73545434.6076106</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>88550227.6723808</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>88144610.1292895</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>105920545.767369</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>111615432.318358</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1959.46232168832</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1968.16115417851</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1936.51805188317</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1927.5800775425</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1879.76241336751</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1897.86473149492</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1897.82928543195</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1866.14374123625</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1987.87827539188</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>1939.73583244229</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1927.15151843965</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1940.55708968664</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1929.94137516015</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>1923.23521916412</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1922.78815628043</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1965.15260143407</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1974.00636244645</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1941.87540759805</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1931.38804914045</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1882.1268250586</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1899.70555776511</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1900.71242194305</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1870.22197612326</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1990.10719777356</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1943.24354564344</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1928.03698635803</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1941.25857367451</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1931.96807997782</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1923.09864318972</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1918.73906912805</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2044.85235715953</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2311.91821551519</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2649.02525917663</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>3427.55295975827</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>4648.58415467507</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>5966.55508186485</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>7157.17326402506</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10210.1971237349</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>12048.4785495379</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>9016.08500022137</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>10236.3842307762</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>12946.5473834591</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>13828.610795824</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>14439.7172992492</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>14718.872659528</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>247354456.06205</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>281423446.974008</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>304048122.028768</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>337913767.010866</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>368632414.933064</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>422574603.724663</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>435151919.613958</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>440352489.722003</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>475302279.028324</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>380559856.132251</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>404878653.126915</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>467712160.765006</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>556365386.800535</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>540165234.692693</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>545103048.537505</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3192.94631997366</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3655.34601000342</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4009.86976876754</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5162.73657779691</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>7037.30152642242</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>8550.50328483256</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>11431.393623958</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>15495.9423807095</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>16043.5415912653</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>9437.30289278005</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10590.8330880897</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>14319.7648416842</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>15129.6042609687</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>15481.1737017266</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>15572.0144618194</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1816.292</t>
+          <t>484880252.785577</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1860.284</t>
+          <t>523964571.344253</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1859.229</t>
+          <t>579953092.865867</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1866.59</t>
+          <t>693331556.155156</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1826.228</t>
+          <t>778674213.935068</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1855.1</t>
+          <t>828454606.758305</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1967.37</t>
+          <t>992357307.933967</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1998.781</t>
+          <t>1055117537.72631</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2103.105</t>
+          <t>936950269.879259</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1750.493</t>
+          <t>591589236.66253</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1610.913</t>
+          <t>563999771.083915</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1645.547</t>
+          <t>725384463.266487</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1690.105</t>
+          <t>814734590.964704</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1714.481</t>
+          <t>780036875.483787</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1723.085</t>
+          <t>841931678.651879</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1535.709</t>
+          <t>-1148.09396281412</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1571.557</t>
+          <t>-1343.42779448822</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1589.281</t>
+          <t>-1360.84450959091</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1615.794</t>
+          <t>-1735.18361803864</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1583.963</t>
+          <t>-2388.71737174735</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1634.536</t>
+          <t>-2583.94820296771</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1728.467</t>
+          <t>-4274.22035993296</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1770.056</t>
+          <t>-5285.7452569746</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1880.672</t>
+          <t>-3995.06304172735</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1541.993</t>
+          <t>-421.217892558676</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1420.831</t>
+          <t>-354.448857313498</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1454.661</t>
+          <t>-1373.2174582251</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1491.285</t>
+          <t>-1300.99346514474</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1509.355</t>
+          <t>-1041.4564024774</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1520.214</t>
+          <t>-853.141802291406</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2149.848</t>
+          <t>-237525796.723527</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2199.587</t>
+          <t>-242541124.370245</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2187.453</t>
+          <t>-275904970.837099</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2297.286</t>
+          <t>-355417789.14429</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2211.875</t>
+          <t>-410041799.002003</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2235.748</t>
+          <t>-405880003.033642</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2466.482</t>
+          <t>-557205388.320009</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2446.104</t>
+          <t>-614765048.004304</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2434.457</t>
+          <t>-461647990.850935</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1872.696</t>
+          <t>-211029380.530279</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1707.733</t>
+          <t>-159121117.957</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1883.878</t>
+          <t>-257672302.501481</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1974.695</t>
+          <t>-258369204.164169</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1935.881</t>
+          <t>-239871640.791093</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1704.145</t>
+          <t>-296828630.114374</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3326.75543314003</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>3512.90144</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>3944.00304</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>4683.54948783404</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>5750.38897983949</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>6382.33609506918</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>7694.36762889546</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>11185.0380560226</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>13391.3639935617</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>10007.3674443006</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>8890.01163</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>10213.3504339611</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>10209.7149505118</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>10760.8505288797</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>10973.9204021916</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1087.065</t>
+          <t>0.153109426824248</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1133.508</t>
+          <t>0.164891234140197</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1110.253</t>
+          <t>0.199820707929425</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1104.928</t>
+          <t>0.209611323524506</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1037.766</t>
+          <t>0.210544180624967</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1029.682</t>
+          <t>0.200471019046288</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1118.239</t>
+          <t>0.194599741680984</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1074.641</t>
+          <t>0.172497698185468</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1112.889</t>
+          <t>0.150523097599112</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>886.09</t>
+          <t>0.140450127373481</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>815.239</t>
+          <t>0.134885763183047</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>851.159</t>
+          <t>0.153645048478415</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>868.637</t>
+          <t>0.151497649538773</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>876.294</t>
+          <t>0.145954804592771</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>867.908</t>
+          <t>0.139808752140959</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3282.8634921583</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3362.80295462533</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3660.65738905393</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4532.32639060765</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>5539.43960164663</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>6841.8139681184</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>8928.31868381733</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13601.7250856622</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16877.2449687495</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11912.5949263967</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>9947.65390490821</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11109.9993304544</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11112.5609327101</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12243.4944816405</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13091.9024182605</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>576.972</t>
+          <t>3660.86046100367</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>587.41</t>
+          <t>3721.90352958466</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>578.206</t>
+          <t>4023.41127999094</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>620.21</t>
+          <t>4966.50457499411</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>599.238</t>
+          <t>6173.60352950848</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>625.266</t>
+          <t>7586.10005956143</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>730.118</t>
+          <t>9898.27308660839</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>798.811</t>
+          <t>15089.9061746681</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>796.407</t>
+          <t>18485.206695062</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>568.084</t>
+          <t>13198.3879217523</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>436.132</t>
+          <t>11185.2095491152</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>458.665</t>
+          <t>12374.6873478486</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>467.138</t>
+          <t>12370.6944229751</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>470.786</t>
+          <t>13707.9732139619</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>458.546</t>
+          <t>14713.5898656293</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>166.17</t>
+          <t>22538.3633860872</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>167.54</t>
+          <t>23138.6393275626</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>174.86</t>
+          <t>23153.8774156127</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>160.52</t>
+          <t>26947.8853815616</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>164.33</t>
+          <t>32516.2005095119</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>161.41</t>
+          <t>37770.2201613247</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>136.74</t>
+          <t>47508.6885524661</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>121.59</t>
+          <t>72491.309786885</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>136.14</t>
+          <t>91533.8330476895</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>171.44</t>
+          <t>73959.9939502697</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>225.78</t>
+          <t>73304.3094847676</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>217.15</t>
+          <t>82569.9458065045</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>219.24</t>
+          <t>84429.6158581416</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>220.6</t>
+          <t>90543.0905228617</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>231.53</t>
+          <t>93269.5045477395</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7.172</t>
+          <t>6875.39623959444</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>7091.13687202196</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6.087</t>
+          <t>7329.96950935195</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>7985.0234268118</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.946</t>
+          <t>8629.40691779396</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.547</t>
+          <t>10111.7148672156</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>11770.4337037434</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>13380.5942626446</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>13649.8962288275</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.173</t>
+          <t>10982.9484517509</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>9776.00854886447</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>9713.38504997953</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>10303.9826288826</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.807</t>
+          <t>10909.1765735617</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>11621.1551669598</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6200.04004864035</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6444.08438114871</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>6699.22203209689</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7296.34918549186</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>7803.56465814864</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>9155.17425731366</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>10667.0593850411</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>12078.0193165578</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>12446.914684351</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>9839.67743781578</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>8694.82846253692</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>8721.74685822595</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>9232.43463888901</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>9698.70812760049</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>10273.919362666</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3450.83589960043</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3815.35879504669</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4626.62417649887</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5648.58192101582</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6846.09679331231</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>7571.83452534342</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>9245.17851991221</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>12504.5840766873</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>13777.9560854582</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10387.6905708572</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>9887.70772945917</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>12686.4633263005</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>12790.8883539699</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>13215.1990844898</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>13039.893043625</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1535709000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1571557000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1589281000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1615794000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1583963000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1634536000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1728467000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1770056000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1880672000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1541993000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1420831000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1454661000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1491285000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1509355000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1520214000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1816292291.87544</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1860283855.90591</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1859229190.25067</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1866589980.09179</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1826227658.35436</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1855100471.26879</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1967370406.58059</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1998781034.76197</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2103105484.46315</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1750493218.35106</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1610913462.84186</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1645546655.14667</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1690104996.0454</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1714480902.3765</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1723085246.24906</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1087064917.46053</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1133508142.51104</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1110252531.21965</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1104927915.29629</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1037766385.10905</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1029681866.73143</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1118239406.31331</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1074641426.34498</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1112889284.38409</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>886090210.364711</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>815238827.058381</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>851158919.574799</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>868637297.450085</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>876293996.157103</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>867908198.153711</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>924250</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>942390</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>957440</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>966450</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>970300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>976520</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1035070</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1068740</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1056780</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>900810</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>835520</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>847670</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>874810</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>891520</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>898030</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>783740</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>798490</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>820690</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>838250</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>842640</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>861250</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>910760</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>948510</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>946070</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>794950</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>737270</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>749610</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>772710</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>784800</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>790630</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1816292291.87544</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1860283855.90591</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1859229190.25067</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1866589980.09179</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1826227658.35436</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1855100471.26879</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1967370406.58059</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1998781034.76197</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2103105484.46315</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1750493218.35106</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1610913462.84186</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1645546655.14667</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1690104996.0454</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1714480902.3765</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1723085246.24906</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1535709000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1571557000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1589281000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1615794000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1583963000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1634536000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1728467000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1770056000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1880672000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1541993000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1420831000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1454661000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1491285000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1509355000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1520214000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>15754.5670253981</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>16410.0788</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18409.4136</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>23057.0232321462</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>28900.4797995319</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>33959.7685429513</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>44468.6776307872</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>61655.7183253122</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>71521.3882057261</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>51904.869698414</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>49324.52448</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>58585.339919238</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>59343.4680153342</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>63011.0093653305</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>64725.6628781127</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7111.79530539807</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7537.10092</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>8650.06512</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>10615.5200321462</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>13019.3597195319</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15157.9340629513</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>19142.3467107872</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>27593.9965753122</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>32262.9416857261</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>23585.547898414</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>21072.66435</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>25061.107919238</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>25162.0064153342</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>26922.6808753305</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>27753.6149885203</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>49051.6946157167</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>48770.2767553794</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>44692.7543703671</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>44199.7439390128</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>46114.4686122842</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>50482.6019108886</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>53231.4985974849</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>63409.356716166</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>66914.1891542256</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>62339.4268614951</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>64070.8177449476</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>63936.0668893426</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>68274.4987707923</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>69446.7655505068</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>70128.6985037219</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
